--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Solal est au parc avec maman. Maëlys est près du bac. Solal va proposer le seau. Il dit : tu viens ? Maëlys dit : je regarde. Solal accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ? Maëlys dit : plus tard. Solal dit : d'accord.</t>
+          <t>Solal est au parc avec maman. Maëlys est près du bac. Solal va proposer le seau. Tu viens ? Je regarde. Solal accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ? Plus tard. D'accord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Solal est au parc avec maman. Maëlys est près du bac. Solal va proposer le seau.
+narrateur|Tu viens ?
+copine|Je regarde.
+narrateur|Solal accepte.
+maman|On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard.
+narrateur|Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ?
+copine|Plus tard.
+enfant-m|D'accord.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Solal invite Maëlys. Que fait-il si Maëlys dit non ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Solal a su proposer. Il a su accepter plusieurs réponses.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Solal donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 enfant-m|D'accord.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Solal invite Maëlys. Que fait-il si Maëlys dit non ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Solal a su proposer. Il a su accepter plusieurs réponses.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Maman range le seau. Solal donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Solal propose le bac, sans forcer</t>
+          <t>Aniss propose le seau rouge</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIF.BES.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Aniss veut creuser au bac. Il propose le seau à Chouchou. Chouchou regarde, puis dit plus tard. Aniss accepte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Solal est au parc avec maman. Maëlys est près du bac. Solal va proposer le seau. Tu viens ? Je regarde. Solal accepte. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ? Plus tard. D'accord.</t>
+          <t>La pluie vient de s'arrêter. Le parc sent la terre mouillée. Des gouttes tombent encore du toboggan. Elles tapent le bord du bac. Le banc de bois est sombre et froid. Un oiseau secoue ses plumes grises. Sur le chemin, des flaques brillent. Maman porte un sac bleu, un peu lourd. Dans le sac, un seau rouge attend. Une petite pelle verte aussi. En ce moment, Aniss marche vers le bac. Maman, le sable est tout mouillé ! Oui, Aniss. Il est frais, ce matin. Tu veux creuser un peu ? Oui. Aniss pose le seau près du bac. Le sable colle à ses doigts. Il est brun, doux, un peu froid. Chouchou est déjà là, au bord. Ses pieds restent sur l'herbe. Aniss le voit. Tu viens ? On peut creuser avec le seau. Je regarde. Aniss écoute. D'accord. Tu as proposé, Aniss. Chouchou regarde. C'est une réponse. Aniss creuse un petit trou. Le seau fait un bruit mou. Chouchou reste sur l'herbe. Il regarde le trou grandir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Solal est au parc avec maman. Maëlys est près du bac. Solal va proposer le seau.
-narrateur|Tu viens ?
-copine|Je regarde.
-narrateur|Solal accepte.
-maman|On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard.
-narrateur|Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ?
-copine|Plus tard.
-enfant-m|D'accord.</t>
+          <t>narrateur|La pluie vient de s'arrêter.
+narrateur|Le parc sent la terre mouillée.
+narrateur|Des gouttes tombent encore du toboggan.
+narrateur|Elles tapent le bord du bac.
+narrateur|Le banc de bois est sombre et froid.
+narrateur|Un oiseau secoue ses plumes grises.
+narrateur|Sur le chemin, des flaques brillent.
+narrateur|Maman porte un sac bleu, un peu lourd.
+narrateur|Dans le sac, un seau rouge attend.
+narrateur|Une petite pelle verte aussi.
+narrateur|En ce moment, Aniss marche vers le bac.
+enfant-m|Maman, le sable est tout mouillé !
+maman|Oui, Aniss.
+maman|Il est frais, ce matin.
+maman|Tu veux creuser un peu ?
+enfant-m|Oui.
+narrateur|Aniss pose le seau près du bac.
+narrateur|Le sable colle à ses doigts.
+narrateur|Il est brun, doux, un peu froid.
+narrateur|Chouchou est déjà là, au bord.
+narrateur|Ses pieds restent sur l'herbe.
+narrateur|Aniss le voit.
+enfant-m|Tu viens ?
+enfant-m|On peut creuser avec le seau.
+copain|Je regarde.
+narrateur|Aniss écoute.
+enfant-m|D'accord.
+maman|Tu as proposé, Aniss.
+maman|Chouchou regarde.
+maman|C'est une réponse.
+narrateur|Aniss creuse un petit trou.
+narrateur|Le seau fait un bruit mou.
+narrateur|Chouchou reste sur l'herbe.
+narrateur|Il regarde le trou grandir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Solal invite Maëlys. Que fait-il si Maëlys dit non ?</t>
+          <t>Aniss invite Chouchou. Que fait-il si Chouchou dit non ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1550,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Solal invite Maëlys. Que fait-il si Maëlys dit non ?</t>
+          <t>narrateur|Aniss invite Chouchou.
+narrateur|Que fait-il si Chouchou dit non ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Solal a su proposer. Il a su accepter plusieurs réponses.</t>
+          <t>Aniss remplit le seau rouge. Le sable glisse, tout humide. Il propose encore, tout doux. Plus tard, tu viens ? Plus tard. D'accord. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Bravo, Aniss. Tu as fait du bon travail. Chouchou avance d'un pas. Il ne touche pas le seau. Aniss continue de creuser. Tu as fini de proposer tout doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1723,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Solal a su proposer. Il a su accepter plusieurs réponses.</t>
+          <t>narrateur|Aniss remplit le seau rouge.
+narrateur|Le sable glisse, tout humide.
+narrateur|Il propose encore, tout doux.
+enfant-m|Plus tard, tu viens ?
+copain|Plus tard.
+enfant-m|D'accord.
+maman|On peut proposer.
+maman|On peut accepter plusieurs réponses.
+maman|Oui.
+maman|Non.
+maman|Regarder.
+maman|Plus tard.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Chouchou avance d'un pas.
+narrateur|Il ne touche pas le seau.
+narrateur|Aniss continue de creuser.
+maman|Tu as fini de proposer tout doux ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Solal donne la main.</t>
+          <t>Le soleil revient un peu. Une goutte tombe encore du toboggan. On range le seau ? Oui. Aniss verse le sable. Il remet le seau dans le sac. Chouchou pose la pelle verte. Leurs chaussures sont mouillées. Aniss tend la main à maman. Bravo. Tu as proposé. Tu as accepté. On rentre ? Oui. Le parc redevient calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,10 +1909,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Solal donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le soleil revient un peu.
+narrateur|Une goutte tombe encore du toboggan.
+maman|On range le seau ?
+enfant-m|Oui.
+narrateur|Aniss verse le sable.
+narrateur|Il remet le seau dans le sac.
+narrateur|Chouchou pose la pelle verte.
+narrateur|Leurs chaussures sont mouillées.
+narrateur|Aniss tend la main à maman.
+maman|Bravo.
+maman|Tu as proposé.
+maman|Tu as accepté.
+maman|On rentre ?
+enfant-m|Oui.
+narrateur|Le parc redevient calme.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1875,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai proposé le seau. Chouchou a regardé. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2095,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai proposé le seau.
+enfant-m|Chouchou a regardé.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie vient de s'arrêter. Le parc sent la terre mouillée. Des gouttes tombent encore du toboggan. Elles tapent le bord du bac. Le banc de bois est sombre et froid. Un oiseau secoue ses plumes grises. Sur le chemin, des flaques brillent. Maman porte un sac bleu, un peu lourd. Dans le sac, un seau rouge attend. Une petite pelle verte aussi. En ce moment, Aniss marche vers le bac. Maman, le sable est tout mouillé ! Oui, Aniss. Il est frais, ce matin. Tu veux creuser un peu ? Oui. Aniss pose le seau près du bac. Le sable colle à ses doigts. Il est brun, doux, un peu froid. Chouchou est déjà là, au bord. Ses pieds restent sur l'herbe. Aniss le voit. Tu viens ? On peut creuser avec le seau. Je regarde. Aniss écoute. D'accord. Tu as proposé, Aniss. Chouchou regarde. C'est une réponse. Aniss creuse un petit trou. Le seau fait un bruit mou. Chouchou reste sur l'herbe. Il regarde le trou grandir.</t>
+          <t>La pluie vient de s'arrêter. Le parc sent la terre mouillée. Des gouttes tombent encore du toboggan. Elles tapent le bord du bac. Le banc de bois est sombre et froid. Un oiseau secoue ses plumes grises. Sur le chemin, des flaques brillent. Maman porte un sac bleu, un peu lourd. Dans le sac, un seau rouge attend. Une petite pelle verte aussi. En ce moment, Aniss marche vers le bac. Maman, le sable est tout mouillé ! Oui, Aniss. Il est frais, ce matin. Tu veux creuser un peu ? Oui. Aniss pose le seau près du bac. Le sable colle à ses doigts. Il est brun, doux, un peu froid. Chouchou est déjà là, au bord. Ses pieds restent sur l'herbe. Aniss le voit. Tu viens ? On peut creuser avec le seau. Je regarde. Aniss écoute. D'accord. Tu as proposé, Aniss. Chouchou regarde. C'est une réponse. Aniss creuse un petit trou. Le seau fait un bruit mou. Une feuille collée au sable se décolle. Chouchou reste sur l'herbe. Il regarde le trou grandir. Un oiseau reprend son chant. Le trou est déjà profond, dis donc. Il est froid, le sable. Oui. Tu continues ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1361,8 +1361,15 @@
 maman|C'est une réponse.
 narrateur|Aniss creuse un petit trou.
 narrateur|Le seau fait un bruit mou.
+narrateur|Une feuille collée au sable se décolle.
 narrateur|Chouchou reste sur l'herbe.
-narrateur|Il regarde le trou grandir.</t>
+narrateur|Il regarde le trou grandir.
+narrateur|Un oiseau reprend son chant.
+maman|Le trou est déjà profond, dis donc.
+enfant-m|Il est froid, le sable.
+maman|Oui.
+maman|Tu continues ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1579,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss remplit le seau rouge. Le sable glisse, tout humide. Il propose encore, tout doux. Plus tard, tu viens ? Plus tard. D'accord. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Bravo, Aniss. Tu as fait du bon travail. Chouchou avance d'un pas. Il ne touche pas le seau. Aniss continue de creuser. Tu as fini de proposer tout doux ? Oui, maman.</t>
+          <t>Aniss remplit le seau rouge. Le sable glisse, tout humide. Il propose encore, tout doux. Plus tard, tu viens ? Plus tard. D'accord. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Bravo, Aniss. Tu as fait du bon travail. Chouchou avance d'un pas. Il ne touche pas le seau. Aniss continue de creuser. Il verse un seau, puis un autre. La colline de sable grandit. Chouchou avance encore un peu. Il reste à regarder. Regarder, c'est bien aussi. Tu as fini de proposer tout doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1740,6 +1747,11 @@
 narrateur|Chouchou avance d'un pas.
 narrateur|Il ne touche pas le seau.
 narrateur|Aniss continue de creuser.
+narrateur|Il verse un seau, puis un autre.
+narrateur|La colline de sable grandit.
+narrateur|Chouchou avance encore un peu.
+narrateur|Il reste à regarder.
+maman|Regarder, c'est bien aussi.
 maman|Tu as fini de proposer tout doux ?
 enfant-m|Oui, maman.</t>
         </is>
@@ -2121,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2176,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aniss propose le seau rouge</t>
+          <t>Les bateaux de la cour</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Après la pluie, Aniss veut creuser au bac. Il propose le seau à Chouchou. Chouchou regarde, puis dit plus tard. Aniss accepte.</t>
+          <t>Aniss veut faire courir ses bateaux de papier dans la flaque de la cour. Chouchou regarde, puis dit plus tard. Aniss accepte, dégage le bateau d'une feuille, et les deux sèchent sur le rebord.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie vient de s'arrêter. Le parc sent la terre mouillée. Des gouttes tombent encore du toboggan. Elles tapent le bord du bac. Le banc de bois est sombre et froid. Un oiseau secoue ses plumes grises. Sur le chemin, des flaques brillent. Maman porte un sac bleu, un peu lourd. Dans le sac, un seau rouge attend. Une petite pelle verte aussi. En ce moment, Aniss marche vers le bac. Maman, le sable est tout mouillé ! Oui, Aniss. Il est frais, ce matin. Tu veux creuser un peu ? Oui. Aniss pose le seau près du bac. Le sable colle à ses doigts. Il est brun, doux, un peu froid. Chouchou est déjà là, au bord. Ses pieds restent sur l'herbe. Aniss le voit. Tu viens ? On peut creuser avec le seau. Je regarde. Aniss écoute. D'accord. Tu as proposé, Aniss. Chouchou regarde. C'est une réponse. Aniss creuse un petit trou. Le seau fait un bruit mou. Une feuille collée au sable se décolle. Chouchou reste sur l'herbe. Il regarde le trou grandir. Un oiseau reprend son chant. Le trou est déjà profond, dis donc. Il est froid, le sable. Oui. Tu continues ? Oui.</t>
+          <t>Le zinc de la gouttière sent le métal froid. Une goutte tombe encore. Elle fait un rond dans la flaque. Les dalles de la cour sont sombres. Un escargot avance sur une fissure. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'escargot, Aniss ? Oui, maman. Il a une petite maison. Oui. On le laisse tout doux. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir. Le long des dalles ? Oui. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Tout doux. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Aniss le voit. Tu viens ? On fait courir les bateaux. Je regarde. Aniss écoute. D'accord. On peut proposer. Tu as proposé, Aniss. Aniss pousse le bateau du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, tout lent. Il laisse passer ! Oui. Une feuille collée barre le chemin. Le bateau s'arrête. Il est coincé. Tu peux le dégager. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Plus tard. D'accord. La feuille est juste devant. Le zinc goutte encore une fois. Le rond tremble, puis s'arrête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Solal est au parc avec maman. Maëlys est près du bac. Solal va &lt;emphasis level="moderate"&gt;proposer&lt;/emphasis&gt; le seau. Il dit : tu viens ? Maëlys dit : je regarde. Solal accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ? Maëlys dit : plus tard. Solal dit : d'accord.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le zinc de la gouttière sent le métal froid. Une goutte tombe encore. Elle fait un rond dans la flaque. Les dalles de la cour sont sombres. Un escargot avance sur une fissure. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'escargot, Aniss ? Oui, maman. Il a une petite maison. Oui. On le laisse tout doux. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir. Le long des dalles ? Oui. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Tout doux. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Aniss le voit. Tu viens ? On fait courir les bateaux. Je regarde. Aniss écoute. D'accord. On peut proposer. Tu as proposé, Aniss. Aniss pousse le bateau du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, tout lent. Il laisse passer ! Oui. Une feuille collée barre le chemin. Le bateau s'arrête. Il est coincé. Tu peux le dégager. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Plus tard. D'accord. La feuille est juste devant. Le zinc goutte encore une fois. Le rond tremble, puis s'arrête.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1329,47 +1329,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La pluie vient de s'arrêter.
-narrateur|Le parc sent la terre mouillée.
-narrateur|Des gouttes tombent encore du toboggan.
-narrateur|Elles tapent le bord du bac.
-narrateur|Le banc de bois est sombre et froid.
-narrateur|Un oiseau secoue ses plumes grises.
-narrateur|Sur le chemin, des flaques brillent.
-narrateur|Maman porte un sac bleu, un peu lourd.
-narrateur|Dans le sac, un seau rouge attend.
-narrateur|Une petite pelle verte aussi.
-narrateur|En ce moment, Aniss marche vers le bac.
-enfant-m|Maman, le sable est tout mouillé !
-maman|Oui, Aniss.
-maman|Il est frais, ce matin.
-maman|Tu veux creuser un peu ?
+          <t>narrateur|Le zinc de la gouttière sent le métal froid.
+narrateur|Une goutte tombe encore.
+narrateur|Elle fait un rond dans la flaque.
+narrateur|Les dalles de la cour sont sombres.
+narrateur|Un escargot avance sur une fissure.
+narrateur|Ça sent la pierre mouillée.
+narrateur|Maman pose un torchon sur le rebord.
+maman|Tu as vu l'escargot, Aniss ?
+enfant-m|Oui, maman.
+enfant-m|Il a une petite maison.
+maman|Oui.
+maman|On le laisse tout doux.
+narrateur|Deux bateaux de papier attendent.
+narrateur|Ils sont un peu froissés.
+narrateur|Papa les a pliés ce matin.
+papa|Ils peuvent flotter dans la flaque.
+enfant-m|Je veux les faire courir.
+maman|Le long des dalles ?
 enfant-m|Oui.
-narrateur|Aniss pose le seau près du bac.
-narrateur|Le sable colle à ses doigts.
-narrateur|Il est brun, doux, un peu froid.
-narrateur|Chouchou est déjà là, au bord.
-narrateur|Ses pieds restent sur l'herbe.
+narrateur|En ce moment, Aniss pose un bateau.
+narrateur|Le papier devient sombre.
+narrateur|Il boit un peu d'eau.
+enfant-m|Il part !
+maman|Tout doux.
+narrateur|Chouchou est sur la marche sèche.
+narrateur|Ses chaussettes restent au sec.
 narrateur|Aniss le voit.
 enfant-m|Tu viens ?
-enfant-m|On peut creuser avec le seau.
+enfant-m|On fait courir les bateaux.
 copain|Je regarde.
 narrateur|Aniss écoute.
 enfant-m|D'accord.
+maman|On peut proposer.
 maman|Tu as proposé, Aniss.
-maman|Chouchou regarde.
-maman|C'est une réponse.
-narrateur|Aniss creuse un petit trou.
-narrateur|Le seau fait un bruit mou.
-narrateur|Une feuille collée au sable se décolle.
-narrateur|Chouchou reste sur l'herbe.
-narrateur|Il regarde le trou grandir.
-narrateur|Un oiseau reprend son chant.
-maman|Le trou est déjà profond, dis donc.
-enfant-m|Il est froid, le sable.
-maman|Oui.
-maman|Tu continues ?
-enfant-m|Oui.</t>
+narrateur|Aniss pousse le bateau du doigt.
+narrateur|Le bateau glisse entre deux dalles.
+narrateur|L'escargot s'écarte, tout lent.
+enfant-m|Il laisse passer !
+papa|Oui.
+narrateur|Une feuille collée barre le chemin.
+narrateur|Le bateau s'arrête.
+enfant-m|Il est coincé.
+maman|Tu peux le dégager.
+narrateur|Aniss cherche autour de la flaque.
+narrateur|Il regarde Chouchou.
+enfant-m|Tu m'aides ?
+copain|Plus tard.
+enfant-m|D'accord.
+papa|La feuille est juste devant.
+narrateur|Le zinc goutte encore une fois.
+narrateur|Le rond tremble, puis s'arrête.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1401,12 +1411,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss invite Chouchou. Que fait-il si Chouchou dit non ?</t>
+          <t>Chouchou dit plus tard. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Solal invite Maëlys. Que fait-il si Maëlys dit non ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou dit plus tard. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1421,7 +1431,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>accepter | proposer | un non | regarder</t>
+          <t>accepter | d'accord | proposer | regarder | plus tard</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1436,7 +1446,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il propose. Maëlys peut regarder. Que fait Solal ?</t>
+          <t>Il accepte. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1557,11 +1567,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aniss invite Chouchou.
-narrateur|Que fait-il si Chouchou dit non ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou dit plus tard.
+narrateur|Que fait Aniss ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1586,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss remplit le seau rouge. Le sable glisse, tout humide. Il propose encore, tout doux. Plus tard, tu viens ? Plus tard. D'accord. On peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Bravo, Aniss. Tu as fait du bon travail. Chouchou avance d'un pas. Il ne touche pas le seau. Aniss continue de creuser. Il verse un seau, puis un autre. La colline de sable grandit. Chouchou avance encore un peu. Il reste à regarder. Regarder, c'est bien aussi. Tu as fini de proposer tout doux ? Oui, maman.</t>
+          <t>Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, tout doux. Le bateau se dégage. Il repart ! Oui. On peut accepter plusieurs réponses. Chouchou reste sur la marche. Il penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Il ne descend pas dans l'eau. Tu as accepté, Aniss. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout. L'escargot a fini sa fissure. Le torchon sent encore l'eau. Tu as fini de les suivre ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Solal a su &lt;emphasis level="moderate"&gt;proposer&lt;/emphasis&gt;. Il a su accepter plusieurs réponses.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, tout doux. Le bateau se dégage. Il repart ! Oui. On peut accepter plusieurs réponses. Chouchou reste sur la marche. Il penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Il ne descend pas dans l'eau. Tu as accepté, Aniss. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout. L'escargot a fini sa fissure. Le torchon sent encore l'eau. Tu as fini de les suivre ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1654,7 +1663,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1730,33 +1739,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss remplit le seau rouge.
-narrateur|Le sable glisse, tout humide.
-narrateur|Il propose encore, tout doux.
-enfant-m|Plus tard, tu viens ?
-copain|Plus tard.
-enfant-m|D'accord.
-maman|On peut proposer.
+          <t>narrateur|Aniss prend une petite brindille.
+narrateur|Elle est lisse, un peu mouillée.
+narrateur|Il pousse la feuille, tout doux.
+narrateur|Le bateau se dégage.
+enfant-m|Il repart !
+maman|Oui.
 maman|On peut accepter plusieurs réponses.
-maman|Oui.
-maman|Non.
-maman|Regarder.
-maman|Plus tard.
-maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
-narrateur|Chouchou avance d'un pas.
-narrateur|Il ne touche pas le seau.
-narrateur|Aniss continue de creuser.
-narrateur|Il verse un seau, puis un autre.
-narrateur|La colline de sable grandit.
-narrateur|Chouchou avance encore un peu.
-narrateur|Il reste à regarder.
-maman|Regarder, c'est bien aussi.
-maman|Tu as fini de proposer tout doux ?
+narrateur|Chouchou reste sur la marche.
+narrateur|Il penche la tête.
+narrateur|Le deuxième bateau attend au sec.
+copain|Je mets une voile ?
+enfant-m|Si tu veux.
+narrateur|Chouchou pose une feuille sèche.
+narrateur|C'est une voile, sur le papier.
+narrateur|Il ne descend pas dans l'eau.
+maman|Tu as accepté, Aniss.
+narrateur|Les deux bateaux glissent.
+narrateur|Ils font deux ronds dans la flaque.
+enfant-m|Ils se croisent !
+papa|Ils arrivent au bout.
+narrateur|L'escargot a fini sa fissure.
+narrateur|Le torchon sent encore l'eau.
+maman|Tu as fini de les suivre ?
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le soleil revient un peu. Une goutte tombe encore du toboggan. On range le seau ? Oui. Aniss verse le sable. Il remet le seau dans le sac. Chouchou pose la pelle verte. Leurs chaussures sont mouillées. Aniss tend la main à maman. Bravo. Tu as proposé. Tu as accepté. On rentre ? Oui. Le parc redevient calme.</t>
+          <t>On pose les bateaux au soleil ? Oui. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Tu as fini de poser les bateaux ? Oui, papa. Les chaussettes de Chouchou sont sèches. Les miennes sont un peu mouillées. On les change après. La cour redevient calme. L'escargot est encore là. Il avance toujours. Tout lent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Solal donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On pose les bateaux au soleil ? Oui. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Tu as fini de poser les bateaux ? Oui, papa. Les chaussettes de Chouchou sont sèches. Les miennes sont un peu mouillées. On les change après. La cour redevient calme. L'escargot est encore là. Il avance toujours. Tout lent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1849,7 +1857,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1921,21 +1929,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le soleil revient un peu.
-narrateur|Une goutte tombe encore du toboggan.
-maman|On range le seau ?
+          <t>maman|On pose les bateaux au soleil ?
 enfant-m|Oui.
-narrateur|Aniss verse le sable.
-narrateur|Il remet le seau dans le sac.
-narrateur|Chouchou pose la pelle verte.
-narrateur|Leurs chaussures sont mouillées.
-narrateur|Aniss tend la main à maman.
-maman|Bravo.
-maman|Tu as proposé.
-maman|Tu as accepté.
-maman|On rentre ?
-enfant-m|Oui.
-narrateur|Le parc redevient calme.</t>
+narrateur|Aniss pose un bateau sur le rebord.
+narrateur|Chouchou pose l'autre.
+narrateur|Le papier sèche un peu.
+papa|Tu as fini de poser les bateaux ?
+enfant-m|Oui, papa.
+maman|Les chaussettes de Chouchou sont sèches.
+enfant-m|Les miennes sont un peu mouillées.
+maman|On les change après.
+narrateur|La cour redevient calme.
+narrateur|L'escargot est encore là.
+papa|Il avance toujours.
+enfant-m|Tout lent.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1967,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai proposé le seau. Chouchou a regardé. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2028,14 +2035,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2107,14 +2114,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai proposé le seau.
+          <t>enfant-m|Mes bateaux ont couru.
 enfant-m|Chouchou a regardé.
-maman|Bravo.
-maman|Tu as fait du bon travail.
+maman|Bravo, Aniss.
+papa|Le rebord a deux bateaux.
+narrateur|Le zinc ne goutte plus.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2206,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -1974,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus. L'histoire est finie.</t>
+          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus. L'histoire est finie.</t>
+          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2118,8 +2118,7 @@
 enfant-m|Chouchou a regardé.
 maman|Bravo, Aniss.
 papa|Le rebord a deux bateaux.
-narrateur|Le zinc ne goutte plus.
-narrateur|L'histoire est finie.</t>
+narrateur|Le zinc ne goutte plus.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2210,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>cour après la pluie, gouttière de zinc, flaque des dalles</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Solal, Maëlys, maman</t>
+          <t>Aniss, Chouchou, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.BES.002-06.xlsx
+++ b/stories/arbres/ATOM-DIF.BES.002-06.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aniss veut faire courir ses bateaux de papier dans la flaque de la cour. Chouchou regarde, puis dit plus tard. Aniss accepte, dégage le bateau d'une feuille, et les deux sèchent sur le rebord.</t>
+          <t>L'air froid glisse le long du zinc. Sur une dalle, un éclat de dalle brille. Aniss veut faire courir les bateaux jusqu'à l'éclat, maintenant. Il propose. Chouchou regarde, puis dit plus tard. Le bateau s'arrête sur une feuille. Sourire parti. Aniss refuse de foncer, accepte, dégage le bateau. Merci vécu. Deux bateaux trop vite : ils se cognent. L'éclat de dalle tient au bout de la flaque.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le zinc de la gouttière sent le métal froid. Une goutte tombe encore. Elle fait un rond dans la flaque. Les dalles de la cour sont sombres. Un escargot avance sur une fissure. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'escargot, Aniss ? Oui, maman. Il a une petite maison. Oui. On le laisse tout doux. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir. Le long des dalles ? Oui. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Tout doux. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Aniss le voit. Tu viens ? On fait courir les bateaux. Je regarde. Aniss écoute. D'accord. On peut proposer. Tu as proposé, Aniss. Aniss pousse le bateau du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, tout lent. Il laisse passer ! Oui. Une feuille collée barre le chemin. Le bateau s'arrête. Il est coincé. Tu peux le dégager. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Plus tard. D'accord. La feuille est juste devant. Le zinc goutte encore une fois. Le rond tremble, puis s'arrête.</t>
+          <t>L'air froid glisse le long du zinc. Aniss connaît cette cour, ses dalles, le bruit de la gouttière. Un détail paraît nouveau, sur une dalle sombre. Au bout de la flaque, un éclat de dalle brille. Il brille, papa. Tu le vois, sur la dalle ? Oui, tout au bout. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'éclat, Aniss ? Oui, maman. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés, ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir, maintenant ! Jusqu'à l'éclat, le long des dalles. Le long des dalles ? Oui, maman. Un escargot avance sur une fissure. Il a une petite maison. On le laisse sur sa fissure ? Oui, papa. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Elle tient le torchon, près du rebord. Tu as le torchon, Chouchou ? Oui, maman. Aniss le voit, sur la marche. Tu viens ? On fait courir les bateaux. Chouchou penche la tête. Elle ne descend pas. Je regarde. Aniss écoute. D'accord. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Aniss pousse trop vite, du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, très lent. Il laisse passer ! Une feuille collée barre le chemin. Le bateau s'arrête, loin de l'éclat. Il est coincé ! Il n'arrive pas au bout. Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'éclat de dalle tremble, puis tient. Les épaules d'Aniss tombent un peu. Papa se baisse à sa hauteur. Tu vois la feuille ? Oui, papa. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Chouchou serre le torchon. Elle reste sur la marche. Plus tard. Aniss ouvre la bouche. Puis il la referme. Ça serre, dans son ventre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le zinc de la gouttière sent le métal froid. Une goutte tombe encore. Elle fait un rond dans la flaque. Les dalles de la cour sont sombres. Un escargot avance sur une fissure. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'escargot, Aniss ? Oui, maman. Il a une petite maison. Oui. On le laisse tout doux. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir. Le long des dalles ? Oui. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Tout doux. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Aniss le voit. Tu viens ? On fait courir les bateaux. Je regarde. Aniss écoute. D'accord. On peut proposer. Tu as proposé, Aniss. Aniss pousse le bateau du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, tout lent. Il laisse passer ! Oui. Une feuille collée barre le chemin. Le bateau s'arrête. Il est coincé. Tu peux le dégager. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Plus tard. D'accord. La feuille est juste devant. Le zinc goutte encore une fois. Le rond tremble, puis s'arrête.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'air froid glisse le long du zinc. Aniss connaît cette cour, ses dalles, le bruit de la gouttière. Un détail paraît nouveau, sur une dalle sombre. Au bout de la flaque, un &lt;emphasis level="moderate"&gt;éclat de dalle&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la dalle ? Oui, tout au bout. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'éclat, Aniss ? Oui, maman. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés, ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir, maintenant ! Jusqu'à l'éclat, le long des dalles. Le long des dalles ? Oui, maman. Un escargot avance sur une fissure. Il a une petite maison. On le laisse sur sa fissure ? Oui, papa. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Elle tient le torchon, près du rebord. Tu as le torchon, Chouchou ? Oui, maman. Aniss le voit, sur la marche. Tu viens ? On fait courir les bateaux. Chouchou penche la tête. Elle ne descend pas. Je regarde. Aniss écoute. D'accord. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Aniss pousse trop vite, du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, très lent. Il laisse passer ! Une feuille collée barre le chemin. Le bateau s'arrête, loin de l'éclat. Il est coincé ! Il n'arrive pas au bout. Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'éclat de dalle tremble, puis tient. Les épaules d'Aniss tombent un peu. Papa se baisse à sa hauteur. Tu vois la feuille ? Oui, papa. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Chouchou serre le torchon. Elle reste sur la marche. Plus tard. Aniss ouvre la bouche. Puis il la referme. Ça serre, dans son ventre.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Solal est au parc avec maman. Maëlys est près du bac. Solal va &lt;emphasis&gt;proposer&lt;/emphasis&gt; le seau. Il dit : tu viens ? Maëlys dit : je regarde. Solal accepte. Maman dit : on peut proposer. On peut accepter plusieurs réponses. Oui. Non. Regarder. Plus tard. Solal creuse. Maëlys regarde. Solal propose encore, tout doux : plus tard ? Maëlys dit : plus tard. Solal dit : d'accord. [pause]</t>
+          <t>L'air froid glisse le long du zinc. Aniss connaît cette cour, ses dalles, le bruit de la gouttière. Un détail paraît nouveau, sur une dalle sombre. Au bout de la flaque, un &lt;emphasis&gt;éclat de dalle&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la dalle ? Oui, tout au bout. Ça sent la pierre mouillée. Maman pose un torchon sur le rebord. Tu as vu l'éclat, Aniss ? Oui, maman. Deux bateaux de papier attendent. Ils sont un peu froissés. Papa les a pliés, ce matin. Ils peuvent flotter dans la flaque. Je veux les faire courir, maintenant ! Jusqu'à l'éclat, le long des dalles. Le long des dalles ? Oui, maman. Un escargot avance sur une fissure. Il a une petite maison. On le laisse sur sa fissure ? Oui, papa. Chouchou est sur la marche sèche. Ses chaussettes restent au sec. Elle tient le torchon, près du rebord. Tu as le torchon, Chouchou ? Oui, maman. Aniss le voit, sur la marche. Tu viens ? On fait courir les bateaux. Chouchou penche la tête. Elle ne descend pas. Je regarde. Aniss écoute. D'accord. En ce moment, Aniss pose un bateau. Le papier devient sombre. Il boit un peu d'eau. Il part ! Aniss pousse trop vite, du doigt. Le bateau glisse entre deux dalles. L'escargot s'écarte, très lent. Il laisse passer ! Une feuille collée barre le chemin. Le bateau s'arrête, loin de l'éclat. Il est coincé ! Il n'arrive pas au bout. Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'éclat de dalle tremble, puis tient. Les épaules d'Aniss tombent un peu. Papa se baisse à sa hauteur. Tu vois la feuille ? Oui, papa. Aniss cherche autour de la flaque. Il regarde Chouchou. Tu m'aides ? Chouchou serre le torchon. Elle reste sur la marche. Plus tard. Aniss ouvre la bouche. Puis il la referme. Ça serre, dans son ventre. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>proposer</t>
+          <t>éclat de dalle</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,65 +1326,82 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_les_bateaux_jusqu_a_l_eclat_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le zinc de la gouttière sent le métal froid.
-narrateur|Une goutte tombe encore.
-narrateur|Elle fait un rond dans la flaque.
-narrateur|Les dalles de la cour sont sombres.
-narrateur|Un escargot avance sur une fissure.
+          <t>narrateur|L'air froid glisse le long du zinc.
+narrateur|Aniss connaît cette cour, ses dalles, le bruit de la gouttière.
+narrateur|Un détail paraît nouveau, sur une dalle sombre.
+narrateur|Au bout de la flaque, un éclat de dalle brille.
+enfant-m|Il brille, papa.
+papa|Tu le vois, sur la dalle ?
+enfant-m|Oui, tout au bout.
 narrateur|Ça sent la pierre mouillée.
 narrateur|Maman pose un torchon sur le rebord.
-maman|Tu as vu l'escargot, Aniss ?
+maman|Tu as vu l'éclat, Aniss ?
 enfant-m|Oui, maman.
-enfant-m|Il a une petite maison.
-maman|Oui.
-maman|On le laisse tout doux.
 narrateur|Deux bateaux de papier attendent.
 narrateur|Ils sont un peu froissés.
-narrateur|Papa les a pliés ce matin.
+narrateur|Papa les a pliés, ce matin.
 papa|Ils peuvent flotter dans la flaque.
-enfant-m|Je veux les faire courir.
+enfant-m|Je veux les faire courir, maintenant !
+enfant-m|Jusqu'à l'éclat, le long des dalles.
 maman|Le long des dalles ?
-enfant-m|Oui.
+enfant-m|Oui, maman.
+narrateur|Un escargot avance sur une fissure.
+enfant-m|Il a une petite maison.
+papa|On le laisse sur sa fissure ?
+enfant-m|Oui, papa.
+narrateur|Chouchou est sur la marche sèche.
+narrateur|Ses chaussettes restent au sec.
+narrateur|Elle tient le torchon, près du rebord.
+maman|Tu as le torchon, Chouchou ?
+enfant-f|Oui, maman.
+narrateur|Aniss le voit, sur la marche.
+enfant-m|Tu viens ?
+enfant-m|On fait courir les bateaux.
+narrateur|Chouchou penche la tête.
+narrateur|Elle ne descend pas.
+enfant-f|Je regarde.
+narrateur|Aniss écoute.
+enfant-m|D'accord.
 narrateur|En ce moment, Aniss pose un bateau.
 narrateur|Le papier devient sombre.
 narrateur|Il boit un peu d'eau.
 enfant-m|Il part !
-maman|Tout doux.
-narrateur|Chouchou est sur la marche sèche.
-narrateur|Ses chaussettes restent au sec.
-narrateur|Aniss le voit.
-enfant-m|Tu viens ?
-enfant-m|On fait courir les bateaux.
-copain|Je regarde.
-narrateur|Aniss écoute.
-enfant-m|D'accord.
-maman|On peut proposer.
-maman|Tu as proposé, Aniss.
-narrateur|Aniss pousse le bateau du doigt.
+narrateur|Aniss pousse trop vite, du doigt.
 narrateur|Le bateau glisse entre deux dalles.
-narrateur|L'escargot s'écarte, tout lent.
+narrateur|L'escargot s'écarte, très lent.
 enfant-m|Il laisse passer !
-papa|Oui.
 narrateur|Une feuille collée barre le chemin.
-narrateur|Le bateau s'arrête.
-enfant-m|Il est coincé.
-maman|Tu peux le dégager.
+narrateur|Le bateau s'arrête, loin de l'éclat.
+enfant-m|Il est coincé !
+enfant-m|Il n'arrive pas au bout.
+narrateur|Le sourire d'Aniss disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|L'éclat de dalle tremble, puis tient.
+narrateur|Les épaules d'Aniss tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu vois la feuille ?
+enfant-m|Oui, papa.
 narrateur|Aniss cherche autour de la flaque.
 narrateur|Il regarde Chouchou.
 enfant-m|Tu m'aides ?
-copain|Plus tard.
-enfant-m|D'accord.
-papa|La feuille est juste devant.
-narrateur|Le zinc goutte encore une fois.
-narrateur|Le rond tremble, puis s'arrête.</t>
+narrateur|Chouchou serre le torchon.
+narrateur|Elle reste sur la marche.
+enfant-f|Plus tard.
+narrateur|Aniss ouvre la bouche.
+narrateur|Puis il la referme.
+narrateur|Ça serre, dans son ventre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>pluie,cour</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1433,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou dit plus tard. Que fait Aniss ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Chouchou dit &lt;emphasis level="moderate"&gt;plus tard&lt;/emphasis&gt;. Que fait Aniss ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Solal invite Maëlys. Que fait-il si Maëlys dit non ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Chouchou dit &lt;emphasis&gt;plus tard&lt;/emphasis&gt;. Que fait Aniss ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1484,7 +1501,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1495,7 +1512,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1510,34 +1527,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>plus tard</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1552,17 +1573,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=chouchou_dit_plus_tard_aniss_accepte; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1595,17 +1616,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, tout doux. Le bateau se dégage. Il repart ! Oui. On peut accepter plusieurs réponses. Chouchou reste sur la marche. Il penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Il ne descend pas dans l'eau. Tu as accepté, Aniss. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout. L'escargot a fini sa fissure. Le torchon sent encore l'eau. Tu as fini de les suivre ? Oui, maman.</t>
+          <t>Aniss veut tirer Chouchou vers l'eau. Viens, maintenant ! Chouchou recule d'un pas, sur la marche. Plus tard. Aniss refuse de foncer. Il referme la main. Il écoute la marche, un instant. D'accord. Papa s'accroupit à la même hauteur. Tu restes près de la flaque ? Oui, papa. Maman se baisse aussi. Merci, Aniss. Maman a entendu toute la phrase. Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, sans se presser. Le bateau se dégage. Il repart ! Il glisse ? Oui, papa. Chouchou reste sur la marche. Elle penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Elle ne descend pas dans l'eau. Tu vois la voile ? Oui, papa. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout ? Presque, papa. L'escargot a fini sa fissure. Le ventre d'Aniss se desserre. Tu as les mains froides ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, tout doux. Le bateau se dégage. Il repart ! Oui. On peut accepter plusieurs réponses. Chouchou reste sur la marche. Il penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Il ne descend pas dans l'eau. Tu as accepté, Aniss. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout. L'escargot a fini sa fissure. Le torchon sent encore l'eau. Tu as fini de les suivre ? Oui, maman.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss veut tirer Chouchou vers l'eau. Viens, maintenant ! Chouchou recule d'un pas, sur la marche. Plus tard. Aniss refuse de foncer. Il referme la main. Il écoute la marche, un instant. &lt;emphasis level="moderate"&gt;D'accord&lt;/emphasis&gt;. Papa s'accroupit à la même hauteur. Tu restes près de la flaque ? Oui, papa. Maman se baisse aussi. Merci, Aniss. Maman a entendu toute la phrase. Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, sans se presser. Le bateau se dégage. Il repart ! Il glisse ? Oui, papa. Chouchou reste sur la marche. Elle penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Elle ne descend pas dans l'eau. Tu vois la voile ? Oui, papa. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout ? Presque, papa. L'escargot a fini sa fissure. Le ventre d'Aniss se desserre. Tu as les mains froides ? Un peu, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Solal a su &lt;emphasis&gt;proposer&lt;/emphasis&gt;. Il a su accepter plusieurs réponses. [pause]</t>
+          <t>Aniss veut tirer Chouchou vers l'eau. Viens, maintenant ! Chouchou recule d'un pas, sur la marche. Plus tard. Aniss refuse de foncer. Il referme la main. Il écoute la marche, un instant. &lt;emphasis&gt;D'accord&lt;/emphasis&gt;. Papa s'accroupit à la même hauteur. Tu restes près de la flaque ? Oui, papa. Maman se baisse aussi. Merci, Aniss. Maman a entendu toute la phrase. Aniss prend une petite brindille. Elle est lisse, un peu mouillée. Il pousse la feuille, sans se presser. Le bateau se dégage. Il repart ! Il glisse ? Oui, papa. Chouchou reste sur la marche. Elle penche la tête. Le deuxième bateau attend au sec. Je mets une voile ? Si tu veux. Chouchou pose une feuille sèche. C'est une voile, sur le papier. Elle ne descend pas dans l'eau. Tu vois la voile ? Oui, papa. Les deux bateaux glissent. Ils font deux ronds dans la flaque. Ils se croisent ! Ils arrivent au bout ? Presque, papa. L'escargot a fini sa fissure. Le ventre d'Aniss se desserre. Tu as les mains froides ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1652,7 +1673,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1660,10 +1681,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1686,30 +1707,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>proposer</t>
+          <t>D'accord</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1718,10 +1739,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1734,35 +1755,56 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_tirer_dit_d_accord; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss prend une petite brindille.
+          <t>narrateur|Aniss veut tirer Chouchou vers l'eau.
+enfant-m|Viens, maintenant !
+narrateur|Chouchou recule d'un pas, sur la marche.
+enfant-f|Plus tard.
+narrateur|Aniss refuse de foncer.
+narrateur|Il referme la main.
+narrateur|Il écoute la marche, un instant.
+enfant-m|D'accord.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu restes près de la flaque ?
+enfant-m|Oui, papa.
+narrateur|Maman se baisse aussi.
+maman|Merci, Aniss.
+narrateur|Maman a entendu toute la phrase.
+narrateur|Aniss prend une petite brindille.
 narrateur|Elle est lisse, un peu mouillée.
-narrateur|Il pousse la feuille, tout doux.
+narrateur|Il pousse la feuille, sans se presser.
 narrateur|Le bateau se dégage.
 enfant-m|Il repart !
-maman|Oui.
-maman|On peut accepter plusieurs réponses.
+papa|Il glisse ?
+enfant-m|Oui, papa.
 narrateur|Chouchou reste sur la marche.
-narrateur|Il penche la tête.
+narrateur|Elle penche la tête.
 narrateur|Le deuxième bateau attend au sec.
-copain|Je mets une voile ?
+enfant-f|Je mets une voile ?
 enfant-m|Si tu veux.
 narrateur|Chouchou pose une feuille sèche.
 narrateur|C'est une voile, sur le papier.
-narrateur|Il ne descend pas dans l'eau.
-maman|Tu as accepté, Aniss.
+narrateur|Elle ne descend pas dans l'eau.
+papa|Tu vois la voile ?
+enfant-m|Oui, papa.
 narrateur|Les deux bateaux glissent.
 narrateur|Ils font deux ronds dans la flaque.
 enfant-m|Ils se croisent !
-papa|Ils arrivent au bout.
+papa|Ils arrivent au bout ?
+enfant-m|Presque, papa.
 narrateur|L'escargot a fini sa fissure.
-narrateur|Le torchon sent encore l'eau.
-maman|Tu as fini de les suivre ?
-enfant-m|Oui, maman.</t>
+narrateur|Le ventre d'Aniss se desserre.
+maman|Tu as les mains froides ?
+enfant-m|Un peu, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>flaque,bateaux</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1831,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On pose les bateaux au soleil ? Oui. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Tu as fini de poser les bateaux ? Oui, papa. Les chaussettes de Chouchou sont sèches. Les miennes sont un peu mouillées. On les change après. La cour redevient calme. L'escargot est encore là. Il avance toujours. Tout lent.</t>
+          <t>Aniss veut les deux bateaux, d'un coup. Tous les deux, jusqu'à l'éclat ! Il pousse trop vite. Les bateaux se cognent. L'un tourne, loin de la dalle. Oh. La voile se couche. Il n'arrive pas ! Aniss avance la main. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Aniss observe la flaque. Il écoute le zinc, une goutte. Au bout, un éclat de dalle luit. Là, sur la dalle. Aniss tient la brindille des deux mains. La brindille est froide, un peu lisse. Elle est froide, papa. Tu le guides jusqu'à l'éclat ? Oui, papa. On avance ? Oui, maman. Aniss pousse sans se presser. Le bateau glisse vers la dalle. L'air froid revient sur les joues. Chouchou souffle, depuis la marche. Fffff. La voile se relève un peu. Il arrive. On marche. Le papier touche l'éclat, tout au bout.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On pose les bateaux au soleil ? Oui. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Tu as fini de poser les bateaux ? Oui, papa. Les chaussettes de Chouchou sont sèches. Les miennes sont un peu mouillées. On les change après. La cour redevient calme. L'escargot est encore là. Il avance toujours. Tout lent.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss veut les deux bateaux, d'un coup. Tous les deux, jusqu'à l'éclat ! Il pousse trop vite. Les bateaux se cognent. L'un tourne, loin de la dalle. Oh. La voile se couche. Il n'arrive pas ! Aniss avance la main. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Aniss observe la flaque. Il écoute le zinc, une goutte. Au bout, un &lt;emphasis level="moderate"&gt;éclat de dalle&lt;/emphasis&gt; luit. Là, sur la dalle. Aniss tient la brindille des deux mains. La brindille est froide, un peu lisse. Elle est froide, papa. Tu le guides jusqu'à l'éclat ? Oui, papa. On avance ? Oui, maman. Aniss pousse sans se presser. Le bateau glisse vers la dalle. L'air froid revient sur les joues. Chouchou souffle, depuis la marche. Fffff. La voile se relève un peu. Il arrive. On marche. Le papier touche l'éclat, tout au bout.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Solal donne la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Aniss veut les deux bateaux, d'un coup. Tous les deux, jusqu'à l'éclat ! Il pousse trop vite. Les bateaux se cognent. L'un tourne, loin de la dalle. Oh. La voile se couche. Il n'arrive pas ! Aniss avance la main. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Aniss observe la flaque. Il écoute le zinc, une goutte. Au bout, un &lt;emphasis&gt;éclat de dalle&lt;/emphasis&gt; luit. Là, sur la dalle. Aniss tient la brindille des deux mains. La brindille est froide, un peu lisse. Elle est froide, papa. Tu le guides jusqu'à l'éclat ? Oui, papa. On avance ? Oui, maman. Aniss pousse sans se presser. Le bateau glisse vers la dalle. L'air froid revient sur les joues. Chouchou souffle, depuis la marche. Fffff. La voile se relève un peu. Il arrive. On marche. Le papier touche l'éclat, tout au bout. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1846,7 +1888,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1854,10 +1896,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1880,30 +1922,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de dalle</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1912,10 +1954,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1926,28 +1968,50 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=deux_bateaux_trop_vite_il_observe_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On pose les bateaux au soleil ?
-enfant-m|Oui.
-narrateur|Aniss pose un bateau sur le rebord.
-narrateur|Chouchou pose l'autre.
-narrateur|Le papier sèche un peu.
-papa|Tu as fini de poser les bateaux ?
+          <t>narrateur|Aniss veut les deux bateaux, d'un coup.
+enfant-m|Tous les deux, jusqu'à l'éclat !
+narrateur|Il pousse trop vite.
+narrateur|Les bateaux se cognent.
+narrateur|L'un tourne, loin de la dalle.
+enfant-m|Oh.
+narrateur|La voile se couche.
+enfant-m|Il n'arrive pas !
+narrateur|Aniss avance la main.
+narrateur|Puis il s'arrête net.
+enfant-m|Attends, je regarde.
+narrateur|Papa attend, sans parler.
+narrateur|Aniss observe la flaque.
+narrateur|Il écoute le zinc, une goutte.
+narrateur|Au bout, un éclat de dalle luit.
+enfant-m|Là, sur la dalle.
+narrateur|Aniss tient la brindille des deux mains.
+narrateur|La brindille est froide, un peu lisse.
+enfant-m|Elle est froide, papa.
+papa|Tu le guides jusqu'à l'éclat ?
 enfant-m|Oui, papa.
-maman|Les chaussettes de Chouchou sont sèches.
-enfant-m|Les miennes sont un peu mouillées.
-maman|On les change après.
-narrateur|La cour redevient calme.
-narrateur|L'escargot est encore là.
-papa|Il avance toujours.
-enfant-m|Tout lent.</t>
+maman|On avance ?
+enfant-m|Oui, maman.
+narrateur|Aniss pousse sans se presser.
+narrateur|Le bateau glisse vers la dalle.
+narrateur|L'air froid revient sur les joues.
+narrateur|Chouchou souffle, depuis la marche.
+enfant-f|Fffff.
+narrateur|La voile se relève un peu.
+enfant-m|Il arrive.
+papa|On marche.
+narrateur|Le papier touche l'éclat, tout au bout.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>flaque,zinc</t>
         </is>
       </c>
     </row>
@@ -1974,17 +2038,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus.</t>
+          <t>Mes bateaux ont couru, papa. Tu les vois, sur le rebord ? Oui, comme tout à l'heure. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Comme tout à l'heure, papa ! Tu le vois, toi ? Oui, sur la dalle. On est bien, ici. Mes chaussettes sont sèches. Les miennes sont un peu mouillées. On les change après ? Oui, maman. Une goutte quitte le zinc. Elle fait un rond dans la flaque. On le voit, maman. Tu le vois sur la dalle ? Oui, l'éclat. Le soir reste dans l'air. Au bout de la flaque, l'éclat de dalle tient.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mes bateaux ont couru. Chouchou a regardé. Bravo, Aniss. Le rebord a deux bateaux. Le zinc ne goutte plus.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mes bateaux ont couru, papa. Tu les vois, sur le rebord ? Oui, comme tout à l'heure. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Comme tout à l'heure, papa ! Tu le vois, toi ? Oui, sur la dalle. On est bien, ici. Mes chaussettes sont sèches. Les miennes sont un peu mouillées. On les change après ? Oui, maman. Une goutte quitte le zinc. Elle fait un rond dans la flaque. On le voit, maman. Tu le vois sur la dalle ? Oui, l'éclat. Le soir reste dans l'air. Au bout de la flaque, l'&lt;emphasis level="moderate"&gt;éclat de dalle&lt;/emphasis&gt; tient.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mes bateaux ont couru, papa. Tu les vois, sur le rebord ? Oui, comme tout à l'heure. Aniss pose un bateau sur le rebord. Chouchou pose l'autre. Le papier sèche un peu. Comme tout à l'heure, papa ! Tu le vois, toi ? Oui, sur la dalle. On est bien, ici. Mes chaussettes sont sèches. Les miennes sont un peu mouillées. On les change après ? Oui, maman. Une goutte quitte le zinc. Elle fait un rond dans la flaque. On le voit, maman. Tu le vois sur la dalle ? Oui, l'éclat. Le soir reste dans l'air. Au bout de la flaque, l'&lt;emphasis&gt;éclat de dalle&lt;/emphasis&gt; tient.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2031,15 +2095,15 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2051,12 +2115,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2065,17 +2129,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de dalle</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2084,11 +2152,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2097,28 +2165,53 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_au_bout_de_la_flaque; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|Mes bateaux ont couru.
-enfant-m|Chouchou a regardé.
-maman|Bravo, Aniss.
-papa|Le rebord a deux bateaux.
-narrateur|Le zinc ne goutte plus.</t>
+          <t>enfant-m|Mes bateaux ont couru, papa.
+papa|Tu les vois, sur le rebord ?
+enfant-m|Oui, comme tout à l'heure.
+narrateur|Aniss pose un bateau sur le rebord.
+narrateur|Chouchou pose l'autre.
+narrateur|Le papier sèche un peu.
+enfant-m|Comme tout à l'heure, papa !
+papa|Tu le vois, toi ?
+enfant-m|Oui, sur la dalle.
+maman|On est bien, ici.
+enfant-f|Mes chaussettes sont sèches.
+enfant-m|Les miennes sont un peu mouillées.
+maman|On les change après ?
+enfant-m|Oui, maman.
+narrateur|Une goutte quitte le zinc.
+narrateur|Elle fait un rond dans la flaque.
+enfant-m|On le voit, maman.
+maman|Tu le vois sur la dalle ?
+enfant-m|Oui, l'éclat.
+narrateur|Le soir reste dans l'air.
+narrateur|Au bout de la flaque, l'éclat de dalle tient.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>zinc,dalles</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2310,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
